--- a/开发相关/02_参数设置/参数设置.xlsx
+++ b/开发相关/02_参数设置/参数设置.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a320b8631e43c89/epb/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\wanxiang\EPBTest\开发相关\02_参数设置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{657B41B9-DB09-432D-8EDD-DC01F6F31EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4320AC8-8874-46CC-A541-910C633D9A8A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910EC9F8-9FF0-4754-9ED3-B13B1AF8F5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{E5210E87-46FD-4FF7-A108-9319A8C2C25E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -181,6 +181,26 @@
 PeakIgnoreMs</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>正上限时长
+FwdOnLimitMs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反向断电值[反向电流“衰减限值”]
+RevDecayLimitA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反向固定空行程时长
+RevEmptyFixedMs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反衰限制时长
+RevDecayRigidMaxMs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -212,12 +232,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -234,7 +266,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -254,6 +286,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -578,7 +616,7 @@
     <col min="3" max="3" width="13.265625" customWidth="1"/>
     <col min="4" max="4" width="14.86328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.06640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.06640625" customWidth="1"/>
     <col min="7" max="7" width="31.06640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.9296875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.53125" bestFit="1" customWidth="1"/>
@@ -586,38 +624,38 @@
     <col min="11" max="11" width="17.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="27.75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="37.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>31</v>
+      <c r="E1" s="7" t="s">
+        <v>39</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>32</v>
+      <c r="G1" s="7" t="s">
+        <v>40</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>33</v>
+      <c r="H1" s="7" t="s">
+        <v>42</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>34</v>
+      <c r="I1" s="7" t="s">
+        <v>41</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>38</v>
       </c>
     </row>
